--- a/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLVII/LTAIPT_A63F47C.xlsx
+++ b/assets/archivos/TRANSPARENCIA/ART 63 COMUNES 2023/2DO_TRIMESTRE/FRACCIONES XLII-XLVII/FRACC XLVII/LTAIPT_A63F47C.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView xWindow="330" yWindow="495" windowWidth="19815" windowHeight="9405"/>
+    <workbookView xWindow="330" yWindow="555" windowWidth="19815" windowHeight="8385"/>
   </bookViews>
   <sheets>
     <sheet name="Informacion" sheetId="1" r:id="rId1"/>
@@ -103,28 +103,28 @@
     <t>Nota</t>
   </si>
   <si>
-    <t>2022</t>
+    <t>2023</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>E5222BB8A6CE9DA68360D06EED615637</t>
-  </si>
-  <si>
-    <t>01/04/2022</t>
-  </si>
-  <si>
-    <t>30/06/2022</t>
-  </si>
-  <si>
-    <t>Transparencia y Archivo</t>
-  </si>
-  <si>
-    <t>11/07/2022</t>
-  </si>
-  <si>
-    <t>Durante el periodo del 01 de abril del 2022 al 30 de junio del 2022, el Colegio de Bachilleres del Estado de Tlaxcala no publico información respecto a transparencia proactiva debido a que no se generó política en referencia a este tema.</t>
+    <t>61C52E01DF6EF7136885E0A462176DAB</t>
+  </si>
+  <si>
+    <t>01/04/2023</t>
+  </si>
+  <si>
+    <t>30/06/2023</t>
+  </si>
+  <si>
+    <t>Área de Transparencia</t>
+  </si>
+  <si>
+    <t>10/07/2023</t>
+  </si>
+  <si>
+    <t>Durante el periodo del 01 de abril del 2023 al 30 de junio del 2023, el Colegio de Bachilleres del Estado de Tlaxcala no publico información respecto a transparencia proactiva debido a que no se generó política en referencia a este tema.</t>
   </si>
 </sst>
 </file>
@@ -520,7 +520,7 @@
   <dimension ref="A1:I8"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="36" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="35.7109375" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="8" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="36.42578125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="38.5703125" bestFit="1" customWidth="1"/>
@@ -528,7 +528,7 @@
     <col min="6" max="6" width="73.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="206.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="201.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" hidden="1" x14ac:dyDescent="0.25">
